--- a/Team-Data/2011-12/2-19-2011-12.xlsx
+++ b/Team-Data/2011-12/2-19-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
@@ -757,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK2" t="n">
         <v>14</v>
@@ -784,13 +851,13 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>3</v>
@@ -811,7 +878,7 @@
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.517</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J3" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.456</v>
@@ -873,22 +940,22 @@
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O3" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T3" t="n">
         <v>38.8</v>
@@ -897,46 +964,46 @@
         <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="W3" t="n">
         <v>6.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y3" t="n">
         <v>5.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="AA3" t="n">
         <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -954,7 +1021,7 @@
         <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -975,28 +1042,28 @@
         <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -1025,85 +1092,85 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.129</v>
+        <v>0.133</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="J4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.417</v>
+        <v>0.418</v>
       </c>
       <c r="L4" t="n">
         <v>4.3</v>
       </c>
       <c r="M4" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N4" t="n">
-        <v>0.302</v>
+        <v>0.305</v>
       </c>
       <c r="O4" t="n">
         <v>15.2</v>
       </c>
       <c r="P4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.726</v>
+        <v>0.731</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="U4" t="n">
         <v>19.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>5.7</v>
       </c>
       <c r="X4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>86.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14.3</v>
+        <v>-13.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1115,13 +1182,13 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1133,19 +1200,19 @@
         <v>26</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP4" t="n">
         <v>23</v>
       </c>
       <c r="AQ4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
         <v>22</v>
@@ -1157,19 +1224,19 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1367,7 @@
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
         <v>10</v>
@@ -1312,19 +1379,19 @@
         <v>18</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
         <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
         <v>2</v>
@@ -1360,7 +1427,7 @@
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.414</v>
+        <v>0.393</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="L6" t="n">
         <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O6" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.697</v>
+        <v>0.695</v>
       </c>
       <c r="R6" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="T6" t="n">
-        <v>43.3</v>
+        <v>42.9</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
         <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
@@ -1479,31 +1546,31 @@
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>10</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1515,7 +1582,7 @@
         <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>18</v>
@@ -1536,10 +1603,10 @@
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.625</v>
+        <v>0.645</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
@@ -1595,43 +1662,43 @@
         <v>0.441</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R7" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S7" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="T7" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="X7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y7" t="n">
         <v>4.4</v>
@@ -1640,16 +1707,16 @@
         <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1667,13 +1734,13 @@
         <v>16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
       </c>
       <c r="AL7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM7" t="n">
         <v>5</v>
@@ -1682,10 +1749,10 @@
         <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
         <v>17</v>
@@ -1694,19 +1761,19 @@
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1715,7 +1782,7 @@
         <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>0.531</v>
+        <v>0.548</v>
       </c>
       <c r="H8" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I8" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="J8" t="n">
-        <v>80.7</v>
+        <v>80</v>
       </c>
       <c r="K8" t="n">
         <v>0.474</v>
@@ -1780,82 +1847,82 @@
         <v>6.8</v>
       </c>
       <c r="M8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="O8" t="n">
         <v>20.7</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="O8" t="n">
-        <v>20.5</v>
-      </c>
       <c r="P8" t="n">
-        <v>27.9</v>
+        <v>28.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>32.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V8" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W8" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.8</v>
+        <v>103.4</v>
       </c>
       <c r="AC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
         <v>3</v>
       </c>
-      <c r="AD8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2</v>
-      </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
@@ -1873,22 +1940,22 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX8" t="n">
         <v>15</v>
@@ -1897,13 +1964,13 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -1935,97 +2002,97 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.333</v>
+        <v>0.313</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
       </c>
       <c r="I9" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="J9" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.43</v>
+        <v>0.432</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.4</v>
       </c>
       <c r="P9" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.767</v>
+        <v>0.776</v>
       </c>
       <c r="R9" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S9" t="n">
         <v>27.8</v>
       </c>
       <c r="T9" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="U9" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="V9" t="n">
         <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="X9" t="n">
         <v>3.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Z9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AA9" t="n">
         <v>19.2</v>
       </c>
-      <c r="AA9" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AB9" t="n">
-        <v>88.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.7</v>
+        <v>-7.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF9" t="n">
         <v>25</v>
       </c>
       <c r="AG9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2034,28 +2101,28 @@
         <v>26</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
       </c>
       <c r="AM9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>29</v>
@@ -2070,25 +2137,25 @@
         <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC9" t="n">
         <v>27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -2195,22 +2262,22 @@
         <v>-1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
         <v>12</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
         <v>9</v>
@@ -2231,7 +2298,7 @@
         <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ10" t="n">
         <v>15</v>
@@ -2255,7 +2322,7 @@
         <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>2</v>
@@ -2270,7 +2337,7 @@
         <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -2299,106 +2366,106 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>84.2</v>
+        <v>84.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.357</v>
+        <v>0.352</v>
       </c>
       <c r="O11" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="P11" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="R11" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T11" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z11" t="n">
         <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>8</v>
       </c>
       <c r="AI11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
         <v>7</v>
@@ -2407,31 +2474,31 @@
         <v>11</v>
       </c>
       <c r="AN11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV11" t="n">
         <v>15</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2440,10 +2507,10 @@
         <v>18</v>
       </c>
       <c r="AY11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>19</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>29</v>
@@ -2452,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -2481,106 +2548,106 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.613</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J12" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.428</v>
+        <v>0.426</v>
       </c>
       <c r="L12" t="n">
         <v>5.6</v>
       </c>
       <c r="M12" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N12" t="n">
         <v>0.361</v>
       </c>
       <c r="O12" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P12" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y12" t="n">
         <v>5.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>94.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>23</v>
@@ -2589,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO12" t="n">
         <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2604,16 +2671,16 @@
         <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -2622,19 +2689,19 @@
         <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
         <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2783,13 +2850,13 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT13" t="n">
         <v>13</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>14</v>
       </c>
       <c r="AU13" t="n">
         <v>11</v>
@@ -2798,16 +2865,16 @@
         <v>5</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
         <v>18</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.581</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2869,37 +2936,37 @@
         <v>0.45</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
         <v>16.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.297</v>
+        <v>0.301</v>
       </c>
       <c r="O14" t="n">
         <v>16.7</v>
       </c>
       <c r="P14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.74</v>
+        <v>0.742</v>
       </c>
       <c r="R14" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T14" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U14" t="n">
         <v>20.9</v>
       </c>
       <c r="V14" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
         <v>5.8</v>
@@ -2911,28 +2978,28 @@
         <v>3.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA14" t="n">
         <v>19.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>14</v>
@@ -2944,7 +3011,7 @@
         <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL14" t="n">
         <v>24</v>
@@ -2953,19 +3020,19 @@
         <v>19</v>
       </c>
       <c r="AN14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,10 +3041,10 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>29</v>
@@ -2995,10 +3062,10 @@
         <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF15" t="n">
         <v>12</v>
@@ -3135,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3147,7 +3214,7 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS15" t="n">
         <v>23</v>
@@ -3180,7 +3247,7 @@
         <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.781</v>
+        <v>0.774</v>
       </c>
       <c r="H16" t="n">
         <v>48.8</v>
@@ -3230,22 +3297,22 @@
         <v>78.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="L16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4</v>
+        <v>0.404</v>
       </c>
       <c r="O16" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="P16" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="Q16" t="n">
         <v>0.782</v>
@@ -3254,19 +3321,19 @@
         <v>9.9</v>
       </c>
       <c r="S16" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T16" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W16" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X16" t="n">
         <v>4.8</v>
@@ -3278,19 +3345,19 @@
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>103.3</v>
+        <v>103.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>1</v>
@@ -3329,13 +3396,13 @@
         <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
@@ -3350,19 +3417,19 @@
         <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
       </c>
       <c r="BB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.419</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J17" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.424</v>
+        <v>0.426</v>
       </c>
       <c r="L17" t="n">
         <v>6.9</v>
@@ -3421,55 +3488,55 @@
         <v>20.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O17" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P17" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.791</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T17" t="n">
-        <v>41.7</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
@@ -3481,43 +3548,43 @@
         <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM17" t="n">
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
         <v>16</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
         <v>2</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>27</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3529,13 +3596,13 @@
         <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>16</v>
@@ -3544,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,46 +3658,46 @@
         <v>35.1</v>
       </c>
       <c r="J18" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.32</v>
+        <v>0.324</v>
       </c>
       <c r="O18" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P18" t="n">
         <v>26</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.774</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T18" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U18" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="V18" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="W18" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X18" t="n">
         <v>4.3</v>
@@ -3639,19 +3706,19 @@
         <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC18" t="n">
         <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3660,7 +3727,7 @@
         <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
         <v>28</v>
@@ -3669,7 +3736,7 @@
         <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>20</v>
@@ -3681,7 +3748,7 @@
         <v>13</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
@@ -3690,7 +3757,7 @@
         <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
@@ -3705,10 +3772,10 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX18" t="n">
         <v>26</v>
@@ -3717,7 +3784,7 @@
         <v>22</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
@@ -3726,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -3755,97 +3822,97 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
         <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" t="n">
-        <v>0.273</v>
+        <v>0.281</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="J19" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.422</v>
+        <v>0.425</v>
       </c>
       <c r="L19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>24.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="O19" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P19" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="R19" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S19" t="n">
         <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="U19" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V19" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W19" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y19" t="n">
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC19" t="n">
         <v>-6.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3863,7 +3930,7 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,7 +3939,7 @@
         <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>6</v>
@@ -3887,7 +3954,7 @@
         <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>26</v>
@@ -3896,10 +3963,10 @@
         <v>25</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
         <v>13</v>
@@ -3908,7 +3975,7 @@
         <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4033,7 +4100,7 @@
         <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>18</v>
@@ -4048,7 +4115,7 @@
         <v>24</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
@@ -4060,7 +4127,7 @@
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4069,10 +4136,10 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.484</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="J21" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L21" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="M21" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.303</v>
+        <v>0.299</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="P21" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="T21" t="n">
         <v>41.6</v>
       </c>
       <c r="U21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W21" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X21" t="n">
         <v>4.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AA21" t="n">
         <v>22.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>16</v>
@@ -4206,34 +4273,34 @@
         <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>20</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>21</v>
-      </c>
       <c r="AK21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
       </c>
       <c r="AP21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ21" t="n">
         <v>11</v>
@@ -4242,10 +4309,10 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4260,10 +4327,10 @@
         <v>29</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -4301,52 +4368,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.774</v>
+        <v>0.767</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="J22" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="K22" t="n">
         <v>0.475</v>
       </c>
       <c r="L22" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M22" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="P22" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.795</v>
+        <v>0.794</v>
       </c>
       <c r="R22" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="T22" t="n">
         <v>43.5</v>
@@ -4355,31 +4422,31 @@
         <v>18.3</v>
       </c>
       <c r="V22" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="W22" t="n">
         <v>7.7</v>
       </c>
       <c r="X22" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA22" t="n">
         <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.3</v>
+        <v>101.6</v>
       </c>
       <c r="AC22" t="n">
         <v>5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK22" t="n">
         <v>2</v>
@@ -4424,10 +4491,10 @@
         <v>21</v>
       </c>
       <c r="AS22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT22" t="n">
         <v>4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -4483,46 +4550,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" t="n">
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0.625</v>
+        <v>0.645</v>
       </c>
       <c r="H23" t="n">
         <v>48.5</v>
       </c>
       <c r="I23" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="J23" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L23" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M23" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="N23" t="n">
         <v>0.391</v>
       </c>
       <c r="O23" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P23" t="n">
         <v>24.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.653</v>
+        <v>0.658</v>
       </c>
       <c r="R23" t="n">
         <v>10.6</v>
@@ -4531,37 +4598,37 @@
         <v>32.6</v>
       </c>
       <c r="T23" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>15.1</v>
       </c>
       <c r="W23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>5</v>
@@ -4603,34 +4670,34 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
         <v>7</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>19</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
         <v>28</v>
       </c>
       <c r="AX23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ23" t="n">
         <v>5</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -4665,85 +4732,85 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="n">
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>0.625</v>
+        <v>0.645</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J24" t="n">
-        <v>83.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K24" t="n">
         <v>0.453</v>
       </c>
       <c r="L24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M24" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="O24" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="P24" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>33.2</v>
       </c>
       <c r="T24" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="W24" t="n">
         <v>8.5</v>
       </c>
       <c r="X24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="AB24" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>5</v>
@@ -4755,13 +4822,13 @@
         <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
         <v>9</v>
@@ -4770,7 +4837,7 @@
         <v>20</v>
       </c>
       <c r="AM24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN24" t="n">
         <v>8</v>
@@ -4779,22 +4846,22 @@
         <v>30</v>
       </c>
       <c r="AP24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
         <v>29</v>
       </c>
       <c r="AS24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
         <v>19</v>
       </c>
       <c r="G25" t="n">
-        <v>0.406</v>
+        <v>0.387</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J25" t="n">
         <v>81.3</v>
@@ -4880,13 +4947,13 @@
         <v>0.344</v>
       </c>
       <c r="O25" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="P25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="R25" t="n">
         <v>9.9</v>
@@ -4898,13 +4965,13 @@
         <v>40.9</v>
       </c>
       <c r="U25" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V25" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X25" t="n">
         <v>5.3</v>
@@ -4913,19 +4980,19 @@
         <v>4.3</v>
       </c>
       <c r="Z25" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AA25" t="n">
         <v>19</v>
       </c>
-      <c r="AA25" t="n">
-        <v>19.1</v>
-      </c>
       <c r="AB25" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>20</v>
@@ -4934,7 +5001,7 @@
         <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH25" t="n">
         <v>28</v>
@@ -4961,10 +5028,10 @@
         <v>29</v>
       </c>
       <c r="AP25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
@@ -4976,28 +5043,28 @@
         <v>25</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
         <v>22</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA25" t="n">
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
         <v>22</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
@@ -5125,7 +5192,7 @@
         <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK26" t="n">
         <v>16</v>
@@ -5137,13 +5204,13 @@
         <v>14</v>
       </c>
       <c r="AN26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>5</v>
@@ -5152,13 +5219,13 @@
         <v>16</v>
       </c>
       <c r="AS26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
         <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
@@ -5173,7 +5240,7 @@
         <v>18</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
@@ -5229,19 +5296,19 @@
         <v>34.3</v>
       </c>
       <c r="J27" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.408</v>
+        <v>0.409</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M27" t="n">
         <v>19.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.305</v>
+        <v>0.308</v>
       </c>
       <c r="O27" t="n">
         <v>18.4</v>
@@ -5250,34 +5317,34 @@
         <v>24.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R27" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="S27" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T27" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="V27" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
         <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA27" t="n">
         <v>20.9</v>
@@ -5286,28 +5353,28 @@
         <v>93.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
@@ -5328,7 +5395,7 @@
         <v>9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -5337,19 +5404,19 @@
         <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5483,7 +5550,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="n">
         <v>4</v>
@@ -5504,7 +5571,7 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -5513,7 +5580,7 @@
         <v>27</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>10</v>
@@ -5528,19 +5595,19 @@
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX28" t="n">
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
@@ -5674,7 +5741,7 @@
         <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
         <v>22</v>
@@ -5695,13 +5762,13 @@
         <v>14</v>
       </c>
       <c r="AR29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>17</v>
@@ -5716,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5725,7 +5792,7 @@
         <v>26</v>
       </c>
       <c r="BB29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC29" t="n">
         <v>25</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -5757,133 +5824,133 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" t="n">
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0.517</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L30" t="n">
         <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.298</v>
+        <v>0.296</v>
       </c>
       <c r="O30" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P30" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R30" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T30" t="n">
         <v>42.4</v>
       </c>
       <c r="U30" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="V30" t="n">
         <v>14.2</v>
       </c>
       <c r="W30" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
         <v>21.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG30" t="n">
         <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
       </c>
       <c r="AK30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>16</v>
@@ -5892,7 +5959,7 @@
         <v>6</v>
       </c>
       <c r="AW30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX30" t="n">
         <v>3</v>
@@ -5904,7 +5971,7 @@
         <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
@@ -6017,19 +6084,19 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
@@ -6038,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6056,7 +6123,7 @@
         <v>15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>12</v>
@@ -6068,13 +6135,13 @@
         <v>23</v>
       </c>
       <c r="AU31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-19-2011-12</t>
+          <t>2012-02-19</t>
         </is>
       </c>
     </row>
